--- a/data/trans_orig/P79A4_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P79A4_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8999</t>
+          <t>9868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>3352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>82,57%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8467</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10100</t>
+          <t>9400</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>14156</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>635</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>869</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>76,37%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>574</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>828</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3949</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4857</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6162</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>8704</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13953</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11322</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4468</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>745</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
